--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WASHINGTON_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WASHINGTON_2014.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C90">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C126">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C633">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C736">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C737">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C774">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1070">
